--- a/artfynd/A 62690-2025 artfynd.xlsx
+++ b/artfynd/A 62690-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16878709</v>
+        <v>133083609</v>
       </c>
       <c r="B2" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäck från Kårebolssjön, Vrm</t>
+          <t>Kårebolsätern, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413519.9740912929</v>
+        <v>413600</v>
       </c>
       <c r="R2" t="n">
-        <v>6696938.214160163</v>
+        <v>6696917</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,57 +740,191 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
         <v>1</v>
-      </c>
-      <c r="AE2" t="b">
-        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vattendrag</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blockigt vattendrag med trumma under mindre väg. Sjö med damm 50m uppströms.</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>under låga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # under låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Ericsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Therese Ericsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Övervakning av utter i Värmlands län - barmarksinventering</t>
+          <t>Joakim Karlsson, Svenja Neeb, Ossian Fjordefalk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>58164817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kårebolssjön, bäck sydost om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>413520</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6696938</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-02-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-02-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning, äldre spår. Utterkana. Foto finns.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vattendrag</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vattendrag 100 m, nedströmms damm. Vägtrumma (4 m) Blandskog. Inventerad sträcka 20 m nedströmms, 25 m uppströmms.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linn Kilevold, Adam Trapp, Moa Pettersson, Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Övervakning av utter i Värmlands län - vinterspårning</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 62690-2025 artfynd.xlsx
+++ b/artfynd/A 62690-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133083609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,8 +937,17 @@
           <t>Övervakning av utter i Värmlands län - vinterspårning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58164817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>